--- a/docs/eu/StructureDefinition-Observation-resultslab-eu-lab.xlsx
+++ b/docs/eu/StructureDefinition-Observation-resultslab-eu-lab.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-15T17:10:39+02:00</t>
+    <t>2026-03-15T18:11:06+02:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/eu/StructureDefinition-Observation-resultslab-eu-lab.xlsx
+++ b/docs/eu/StructureDefinition-Observation-resultslab-eu-lab.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-15T18:11:06+02:00</t>
+    <t>2026-03-15T21:22:52+02:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1284,7 +1284,7 @@
     <t>valueRatio</t>
   </si>
   <si>
-    <t xml:space="preserve">Ratio {http://hl7.eu/fhir/laboratory/StructureDefinition/Ratio-eu-lab|0.0.1}
+    <t xml:space="preserve">Ratio {http://hl7.eu/fhir/laboratory/StructureDefinition/Ratio-eu-lab|0.0.2}
 </t>
   </si>
   <si>
@@ -1324,7 +1324,7 @@
     <t>valueQuantity</t>
   </si>
   <si>
-    <t xml:space="preserve">Quantity {http://hl7.eu/fhir/laboratory/StructureDefinition/Quantity-eu-lab|0.0.1}
+    <t xml:space="preserve">Quantity {http://hl7.eu/fhir/laboratory/StructureDefinition/Quantity-eu-lab|0.0.2}
 </t>
   </si>
   <si>
